--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_VELABASKET CB SUECA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_VELABASKET CB SUECA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>18.5074</v>
+        <v>23.0348</v>
       </c>
       <c r="E2" t="n">
-        <v>19.5095</v>
+        <v>24.8154</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0021</v>
+        <v>-1.7806</v>
       </c>
       <c r="G2" t="n">
-        <v>8.3703</v>
+        <v>12.6116</v>
       </c>
       <c r="H2" t="n">
-        <v>10.6214</v>
+        <v>15.3472</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.2511</v>
+        <v>-2.7357</v>
       </c>
       <c r="J2" t="n">
-        <v>13.611</v>
+        <v>21.6658</v>
       </c>
       <c r="K2" t="n">
-        <v>12.0874</v>
+        <v>19.0954</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5236</v>
+        <v>2.5706</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.2407</v>
+        <v>-9.0542</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.466</v>
+        <v>-3.7482</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.7747</v>
+        <v>-5.3061</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2006</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2009</v>
+        <v>-8.5684</v>
       </c>
       <c r="R2" t="n">
-        <v>5.4015</v>
+        <v>9.1526</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4781</v>
+        <v>4.4637</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0014</v>
+        <v>4.3184</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5233999999999999</v>
+        <v>0.1451999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>5.458500000000001</v>
+        <v>5.3754</v>
       </c>
       <c r="W2" t="n">
-        <v>6.098100000000001</v>
+        <v>7.399500000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6395000000000001</v>
+        <v>-2.0243</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.9152</v>
+        <v>10.0896</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5831</v>
+        <v>5.0582</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3322</v>
+        <v>5.0313</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3718</v>
+        <v>4.165800000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5528</v>
+        <v>2.1759</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.181</v>
+        <v>1.9899</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5121</v>
+        <v>5.0281</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0263</v>
+        <v>3.4387</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5142</v>
+        <v>1.5896</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1403</v>
+        <v>-0.8623999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5265</v>
+        <v>-1.2627</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6668</v>
+        <v>0.4005000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2004</v>
+        <v>0.7790999999999998</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0009</v>
+        <v>-6.0369</v>
       </c>
       <c r="R3" t="n">
-        <v>4.2012</v>
+        <v>6.8157</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7032</v>
+        <v>4.2195</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8126</v>
+        <v>3.8311</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1094000000000001</v>
+        <v>0.3886000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>3.64</v>
+        <v>0.9253</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2592</v>
+        <v>2.2358</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3807</v>
+        <v>-1.3105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0586</v>
+        <v>7.0185</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0128</v>
+        <v>7.0185</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.954</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.791</v>
+        <v>7.0185</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7472</v>
+        <v>2.1553</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04379999999999984</v>
+        <v>4.8632</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4157</v>
+        <v>7.0185</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1627</v>
+        <v>2.1553</v>
       </c>
       <c r="L4" t="n">
-        <v>2.253</v>
+        <v>4.8632</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.6247</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4155</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2092</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.801</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.0011</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.4337</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6625</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.7712</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9003</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5592999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6995</v>
+        <v>1.3986</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6995</v>
+        <v>0.8167</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.5818000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6995</v>
+        <v>1.1884</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8996999999999999</v>
+        <v>0.9329</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7997</v>
+        <v>0.2556</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6995</v>
+        <v>0.3802</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8996999999999999</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7997</v>
+        <v>-0.5025000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.8080999999999998</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.05020000000000002</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.7579</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.3368</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.4171</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.078</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.4016000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5006</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.9022</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>D. MARTÍNEZ JURADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,61 +874,61 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.167</v>
+        <v>0.6079</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5468000000000001</v>
+        <v>0.6079</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3799</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2524</v>
+        <v>0.6079</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4937</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7461</v>
+        <v>0.6079</v>
       </c>
       <c r="J6" t="n">
-        <v>0.12</v>
+        <v>0.6079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04</v>
+        <v>0.6079</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3724000000000001</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4137</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7861</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6002000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6002000000000001</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1807</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4269</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6076</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09269999999999998</v>
+        <v>0.3526</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6506000000000001</v>
+        <v>-0.1855</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5578000000000001</v>
+        <v>0.5381</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0721</v>
+        <v>0.1934</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.171</v>
+        <v>-0.2053</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9012</v>
+        <v>0.3987</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3435</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3435</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4156</v>
+        <v>0.1934</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5145</v>
+        <v>-0.2053</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9012</v>
+        <v>0.3987</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2006</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2004</v>
+        <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7447</v>
+        <v>0.0866</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5077</v>
+        <v>-0.1855</v>
       </c>
       <c r="U7" t="n">
-        <v>0.237</v>
+        <v>0.2721</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4204000000000001</v>
+        <v>-0.1221</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4204000000000001</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="8">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3404</v>
+        <v>0.2117000000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9606</v>
+        <v>-2.7988</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6202</v>
+        <v>3.0103</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0246</v>
+        <v>-1.2493</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2248</v>
+        <v>-1.3948</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7999000000000001</v>
+        <v>0.1454</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.974</v>
+        <v>-1.1022</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.296</v>
+        <v>-0.5027000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.678</v>
+        <v>-0.5996</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05060000000000001</v>
+        <v>-0.1471000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0713</v>
+        <v>-0.892</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1219</v>
+        <v>0.7450000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6002</v>
+        <v>1.1684</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6002</v>
+        <v>2.3368</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08410000000000001</v>
+        <v>-0.2474</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0134</v>
+        <v>-0.8075</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0707</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.2605</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.713</v>
+        <v>-0.3949000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6546</v>
+        <v>0.9450999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.05840000000000004</v>
+        <v>-1.34</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7109</v>
+        <v>-4.4031</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4972999999999999</v>
+        <v>-3.2915</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2135</v>
+        <v>-1.1115</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1523</v>
+        <v>1.1648</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08179999999999998</v>
+        <v>0.5569000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2341</v>
+        <v>0.6079</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5586</v>
+        <v>-5.5679</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5791000000000001</v>
+        <v>-3.8484</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02060000000000001</v>
+        <v>-1.7194</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6005</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.2842</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6005</v>
+        <v>4.2842</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3429</v>
+        <v>2.4045</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5023</v>
+        <v>2.5639</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8406</v>
+        <v>-0.1595</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2598</v>
+        <v>1.6037</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2598</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1158</v>
+        <v>-1.8611</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4156</v>
+        <v>-0.1841999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7002</v>
+        <v>-1.6769</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0895</v>
+        <v>2.1359</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1273</v>
+        <v>0.5577000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.216799999999999</v>
+        <v>1.5782</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0483</v>
+        <v>6.576000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9225</v>
+        <v>3.1127</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.9707</v>
+        <v>3.4633</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0412</v>
+        <v>-4.44</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2047</v>
+        <v>-2.555</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.246</v>
+        <v>-1.885</v>
       </c>
       <c r="P10" t="n">
-        <v>4.4013</v>
+        <v>-0.7788999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-7.0105</v>
       </c>
       <c r="R10" t="n">
-        <v>5.4016</v>
+        <v>6.2315</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.2273</v>
+        <v>-4.0892</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2867</v>
+        <v>-2.1402</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.9405</v>
+        <v>-1.9489</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2003</v>
+        <v>0.871</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0803</v>
+        <v>2.3906</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.12</v>
+        <v>-1.5195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.797600000000001</v>
+        <v>-3.5383</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1295</v>
+        <v>-3.747</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3318999999999999</v>
+        <v>0.2087</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2175</v>
+        <v>-3.1207</v>
       </c>
       <c r="H11" t="n">
-        <v>0.719</v>
+        <v>-0.8079000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9365</v>
+        <v>-2.3129</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2857000000000003</v>
+        <v>-2.504</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8703</v>
+        <v>-0.09739999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5846</v>
+        <v>-2.4066</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5032</v>
+        <v>-0.6169</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1513</v>
+        <v>-0.7104</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3519</v>
+        <v>0.09350000000000003</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6004</v>
+        <v>2.3369</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.2015</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.601</v>
+        <v>2.3369</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6396</v>
+        <v>-1.5144</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7333999999999999</v>
+        <v>-1.2431</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9062</v>
+        <v>-0.2713</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3401</v>
+        <v>-1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8596999999999999</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.879099999999999</v>
+        <v>-11.5988</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3480999999999996</v>
+        <v>-9.120100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.530900000000001</v>
+        <v>-2.4785</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0181</v>
+        <v>-11.1618</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0067</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.0247</v>
+        <v>-10.2631</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1797000000000002</v>
+        <v>-5.7218</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5647</v>
+        <v>0.7497</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.7444</v>
+        <v>-6.4715</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.8383</v>
+        <v>-5.44</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5581</v>
+        <v>-1.6482</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.2803</v>
+        <v>-3.7917</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.4004</v>
+        <v>6.4263</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.2012</v>
+        <v>-2.5315</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8008</v>
+        <v>8.9579</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7804</v>
+        <v>-6.847</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5137999999999999</v>
+        <v>-2.5952</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2941</v>
+        <v>-4.2517</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6802</v>
+        <v>-0.01640000000000008</v>
       </c>
       <c r="W12" t="n">
-        <v>3.519</v>
+        <v>1.7284</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.1992</v>
+        <v>-1.7448</v>
       </c>
     </row>
     <row r="13">
@@ -1420,148 +1420,304 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.178799999999999</v>
+        <v>-14.8584</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1719</v>
+        <v>-14.0666</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0069</v>
+        <v>-0.7919999999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.135899999999999</v>
+        <v>-8.6014</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5327</v>
+        <v>-3.8628</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.6033</v>
+        <v>-4.7387</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8904</v>
+        <v>-5.6125</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0963</v>
+        <v>-1.5367</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.794</v>
+        <v>-4.0759</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2456</v>
+        <v>-2.9889</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4362</v>
+        <v>-2.3261</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.8092</v>
+        <v>-0.6628000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4001</v>
+        <v>-0.1947999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0009</v>
+        <v>-6.0369</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6008</v>
+        <v>5.8421</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7623</v>
+        <v>-4.3367</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1201</v>
+        <v>-2.873</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6422</v>
+        <v>-1.4635</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8805000000000001</v>
+        <v>-1.7258</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1606</v>
+        <v>0.4558</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.7199</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>P. ANTICH MINGUEZ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VELABASKET CB SUECA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-17.9073</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-12.9281</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-4.9794</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-3.6882</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4.1754</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7808000000000002</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.3565</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-2.5757</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-4.469</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2.8695</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.5997</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-9.1526</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-15.1894</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6.0368</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-3.1128</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.9099</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2.2028</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.9538</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.3906</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-4.3443</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E. MORATA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>VELABASKET CB SUECA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-19.6415</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-5.7358</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-13.9057</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-9.0319</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-3.701</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-5.331</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8766</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.017</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.1405</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-9.9085</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-5.7182</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-4.190399999999999</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-2.5315</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-9.347300000000001</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6.8159</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-2.4639</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1679999999999999</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-2.6319</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-5.6142</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.5668</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-8.181100000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>VELABASKET CB SUECA</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6.415699999999999</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.322</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-9.905900000000001</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-7.288399999999998</v>
-      </c>
-      <c r="H14" t="n">
-        <v>18.742</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-26.0306</v>
-      </c>
-      <c r="J14" t="n">
-        <v>18.7428</v>
-      </c>
-      <c r="K14" t="n">
-        <v>26.6466</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-7.903700000000001</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-26.0312</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-7.904499999999999</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-18.1267</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10.003</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-22.0064</v>
-      </c>
-      <c r="R14" t="n">
-        <v>32.0093</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-4.356799999999999</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.970800000000001</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-9.327500000000001</v>
-      </c>
-      <c r="V14" t="n">
-        <v>8.058300000000003</v>
-      </c>
-      <c r="W14" t="n">
-        <v>14.6146</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-6.5563</v>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-27.0866</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-9.504300000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-17.5829</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-13.3349</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.494000000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-20.8294</v>
+      </c>
+      <c r="J16" t="n">
+        <v>29.15819999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>33.22800000000001</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-4.0698</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-42.49340000000001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-25.7338</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-16.7595</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.9735000000000005</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-62.3156</v>
+      </c>
+      <c r="R16" t="n">
+        <v>61.3419</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-11.02</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.204999999999999</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-12.2245</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-1.758500000000001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>22.4481</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-24.2068</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_VELABASKET CB SUECA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_VELABASKET CB SUECA.xlsx
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>23.0348</v>
+        <v>18.5039</v>
       </c>
       <c r="E2" t="n">
-        <v>24.8154</v>
+        <v>21.9728</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7806</v>
+        <v>-3.469</v>
       </c>
       <c r="G2" t="n">
         <v>12.6116</v>
@@ -610,13 +610,13 @@
         <v>9.1526</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4637</v>
+        <v>-0.06719999999999994</v>
       </c>
       <c r="T2" t="n">
-        <v>4.3184</v>
+        <v>1.4759</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1451999999999999</v>
+        <v>-1.543</v>
       </c>
       <c r="V2" t="n">
         <v>5.3754</v>
@@ -643,13 +643,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10.0896</v>
+        <v>7.437500000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0582</v>
+        <v>2.9751</v>
       </c>
       <c r="F3" t="n">
-        <v>5.0313</v>
+        <v>4.4624</v>
       </c>
       <c r="G3" t="n">
         <v>4.165800000000001</v>
@@ -688,13 +688,13 @@
         <v>6.8157</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2195</v>
+        <v>1.5675</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8311</v>
+        <v>1.7481</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3886000000000001</v>
+        <v>-0.1803999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.9253</v>
@@ -799,13 +799,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3986</v>
+        <v>1.17</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8167</v>
+        <v>0.2048000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5818000000000001</v>
+        <v>0.9653</v>
       </c>
       <c r="G5" t="n">
         <v>1.1884</v>
@@ -844,13 +844,13 @@
         <v>2.3368</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4171</v>
+        <v>0.1885</v>
       </c>
       <c r="T5" t="n">
-        <v>1.078</v>
+        <v>0.4661000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.2777</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4016000000000001</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MARTÍNEZ JURADO</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6079</v>
+        <v>0.6697</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6079</v>
+        <v>1.5583</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.8886999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6079</v>
+        <v>2.1359</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.5577000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6079</v>
+        <v>1.5782</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6079</v>
+        <v>6.576000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3.1127</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6079</v>
+        <v>3.4633</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-4.44</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-2.555</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.885</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.7788999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-7.0105</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>6.2315</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-1.5584</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.3978</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-1.1606</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.871</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.3906</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. FONT FENOLLAR</t>
+          <t>D. MARTÍNEZ JURADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3526</v>
+        <v>0.6079</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1855</v>
+        <v>0.6079</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5381</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1934</v>
+        <v>0.6079</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3987</v>
+        <v>0.6079</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.6079</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6079</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1934</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3987</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0866</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1855</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2721</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1221</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2117000000000002</v>
+        <v>0.3967</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7988</v>
+        <v>-0.0858</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0103</v>
+        <v>0.4825</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2493</v>
+        <v>0.1934</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3948</v>
+        <v>-0.2053</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1454</v>
+        <v>0.3987</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1022</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5027000000000001</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5996</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1471000000000001</v>
+        <v>0.1934</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.892</v>
+        <v>-0.2053</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7450000000000001</v>
+        <v>0.3987</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1684</v>
+        <v>0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3368</v>
+        <v>0.1947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2474</v>
+        <v>0.1306</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8075</v>
+        <v>-0.0858</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2164</v>
       </c>
       <c r="V8" t="n">
-        <v>0.54</v>
+        <v>-0.1221</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2605</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3949000000000001</v>
+        <v>0.3578000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9450999999999999</v>
+        <v>-3.036</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.34</v>
+        <v>3.3937</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4031</v>
+        <v>-1.2493</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.2915</v>
+        <v>-1.3948</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1115</v>
+        <v>0.1454</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1648</v>
+        <v>-1.1022</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5569000000000001</v>
+        <v>-0.5027000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6079</v>
+        <v>-0.5996</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.5679</v>
+        <v>-0.1471000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.8484</v>
+        <v>-0.892</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7194</v>
+        <v>0.7450000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.2842</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>4.2842</v>
+        <v>2.3368</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4045</v>
+        <v>-0.1013</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5639</v>
+        <v>-1.0447</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1595</v>
+        <v>0.9434</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6037</v>
+        <v>0.54</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5005</v>
+        <v>0.2795</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1031</v>
+        <v>0.2605</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8611</v>
+        <v>-1.5715</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1841999999999999</v>
+        <v>-0.3028</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6769</v>
+        <v>-1.269</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1359</v>
+        <v>-4.4031</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5577000000000001</v>
+        <v>-3.2915</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5782</v>
+        <v>-1.1115</v>
       </c>
       <c r="J10" t="n">
-        <v>6.576000000000001</v>
+        <v>1.1648</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1127</v>
+        <v>0.5569000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>3.4633</v>
+        <v>0.6079</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.44</v>
+        <v>-5.5679</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.555</v>
+        <v>-3.8484</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.885</v>
+        <v>-1.7194</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7788999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.0105</v>
+        <v>-4.2842</v>
       </c>
       <c r="R10" t="n">
-        <v>6.2315</v>
+        <v>4.2842</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.0892</v>
+        <v>1.2278</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.1402</v>
+        <v>1.3162</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.9489</v>
+        <v>-0.08850000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>0.871</v>
+        <v>1.6037</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3906</v>
+        <v>1.5005</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5195</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5383</v>
+        <v>-3.2572</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.747</v>
+        <v>-3.3484</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2087</v>
+        <v>0.09109999999999996</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1207</v>
@@ -1312,13 +1312,13 @@
         <v>2.3369</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5144</v>
+        <v>-1.2333</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2431</v>
+        <v>-0.8444</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2713</v>
+        <v>-0.3888</v>
       </c>
       <c r="V11" t="n">
         <v>-1.24</v>
@@ -1345,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.5988</v>
+        <v>-7.1182</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.120100000000001</v>
+        <v>-6.2193</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4785</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-11.1618</v>
@@ -1390,13 +1390,13 @@
         <v>8.9579</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.847</v>
+        <v>-2.3664</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5952</v>
+        <v>0.3055</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.2517</v>
+        <v>-2.672</v>
       </c>
       <c r="V12" t="n">
         <v>-0.01640000000000008</v>
@@ -1423,13 +1423,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.8584</v>
+        <v>-12.2012</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.0666</v>
+        <v>-11.8635</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7919999999999998</v>
+        <v>-0.3375999999999995</v>
       </c>
       <c r="G13" t="n">
         <v>-8.6014</v>
@@ -1468,13 +1468,13 @@
         <v>5.8421</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.3367</v>
+        <v>-1.6793</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.873</v>
+        <v>-0.6698999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4635</v>
+        <v>-1.0093</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7258</v>
@@ -1501,13 +1501,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.9073</v>
+        <v>-15.7118</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.9281</v>
+        <v>-11.7836</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.9794</v>
+        <v>-3.9282</v>
       </c>
       <c r="G14" t="n">
         <v>-3.6882</v>
@@ -1546,13 +1546,13 @@
         <v>6.0368</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.1128</v>
+        <v>-0.9172</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9099</v>
+        <v>0.2345</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2028</v>
+        <v>-1.1517</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9538</v>
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.6415</v>
+        <v>-18.2574</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.7358</v>
+        <v>-4.729</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.9057</v>
+        <v>-13.5286</v>
       </c>
       <c r="G15" t="n">
         <v>-9.0319</v>
@@ -1624,13 +1624,13 @@
         <v>6.8159</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4639</v>
+        <v>-1.0797</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1679999999999999</v>
+        <v>1.175</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.6319</v>
+        <v>-2.2548</v>
       </c>
       <c r="V15" t="n">
         <v>-5.6142</v>
@@ -1657,13 +1657,13 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.0866</v>
+        <v>-21.9553</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.504300000000001</v>
+        <v>-7.031000000000005</v>
       </c>
       <c r="F16" t="n">
-        <v>-17.5829</v>
+        <v>-14.9248</v>
       </c>
       <c r="G16" t="n">
         <v>-13.3349</v>
@@ -1678,7 +1678,7 @@
         <v>29.15819999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>33.22800000000001</v>
+        <v>33.228</v>
       </c>
       <c r="L16" t="n">
         <v>-4.0698</v>
@@ -1702,13 +1702,13 @@
         <v>61.3419</v>
       </c>
       <c r="S16" t="n">
-        <v>-11.02</v>
+        <v>-5.8884</v>
       </c>
       <c r="T16" t="n">
-        <v>1.204999999999999</v>
+        <v>3.678700000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-12.2245</v>
+        <v>-9.566999999999998</v>
       </c>
       <c r="V16" t="n">
         <v>-1.758500000000001</v>
